--- a/product_upload/packages/54/file.xlsx
+++ b/product_upload/packages/54/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -669,7 +674,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -814,7 +819,7 @@
         </is>
       </c>
       <c r="AO2" s="1" t="n">
-        <v>45425.52236111111</v>
+        <v>25569.12552575232</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
@@ -831,6 +836,11 @@
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
+        <is>
+          <t>Amlohope Plus</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
         <is>
           <t>SKU-C4DC60CA9ED5</t>
         </is>
@@ -851,7 +861,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -996,7 +1006,7 @@
         </is>
       </c>
       <c r="AO3" s="1" t="n">
-        <v>45425.52258101852</v>
+        <v>25569.12552575232</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
@@ -1013,6 +1023,11 @@
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
+        <is>
+          <t>Amlohope Plus</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
         <is>
           <t>SKU-F748DFC30DAA</t>
         </is>
@@ -1033,7 +1048,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1180,7 +1195,7 @@
         </is>
       </c>
       <c r="AO4" s="1" t="n">
-        <v>45433.66421296296</v>
+        <v>25569.12552584491</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
@@ -1197,6 +1212,11 @@
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
+        <is>
+          <t>Glycelax</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
         <is>
           <t>SKU-B87A518D4CFF</t>
         </is>
@@ -1217,7 +1237,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1385,6 +1405,11 @@
         </is>
       </c>
       <c r="AT5" t="inlineStr">
+        <is>
+          <t>Uxorate</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
         <is>
           <t>SKU-1C0687A9550F</t>
         </is>
@@ -1405,7 +1430,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1565,6 +1590,11 @@
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
+        <is>
+          <t>Uxorate</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
         <is>
           <t>SKU-E5387E0FF161</t>
         </is>
@@ -1585,7 +1615,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1730,7 +1760,7 @@
         </is>
       </c>
       <c r="AO7" s="1" t="n">
-        <v>45574.64369212963</v>
+        <v>25569.12552747685</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
@@ -1751,6 +1781,11 @@
         </is>
       </c>
       <c r="AT7" t="inlineStr">
+        <is>
+          <t>ALUNBRIG</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
         <is>
           <t>SKU-B2535F6D79F8</t>
         </is>
@@ -1771,7 +1806,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1914,7 +1949,7 @@
         </is>
       </c>
       <c r="AO8" s="1" t="n">
-        <v>45445.63918981481</v>
+        <v>25569.1255259838</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
@@ -1927,6 +1962,11 @@
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
+        <is>
+          <t>Milorizast</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
         <is>
           <t>SKU-64495F1FE0EE</t>
         </is>
@@ -1947,7 +1987,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2109,6 +2149,11 @@
         </is>
       </c>
       <c r="AT9" t="inlineStr">
+        <is>
+          <t>Novus</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
         <is>
           <t>SKU-7D1A93249B48</t>
         </is>
@@ -2129,7 +2174,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2287,6 +2332,11 @@
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
+        <is>
+          <t>Novus</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
         <is>
           <t>SKU-7B652E81C973</t>
         </is>
@@ -2307,7 +2357,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2460,7 +2510,7 @@
         </is>
       </c>
       <c r="AO11" s="1" t="n">
-        <v>45655.32334490741</v>
+        <v>25569.12552841435</v>
       </c>
       <c r="AP11" t="n">
         <v>6.800000190734863</v>
@@ -2477,6 +2527,11 @@
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
+        <is>
+          <t>Topferol</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
         <is>
           <t>SKU-167AC44DE90B</t>
         </is>
@@ -2497,7 +2552,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2653,6 +2708,11 @@
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
+        <is>
+          <t>SoiCarby</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
         <is>
           <t>SKU-5EE7D239D3C2</t>
         </is>
@@ -2673,7 +2733,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2837,6 +2897,11 @@
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
+        <is>
+          <t>Debrex</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
         <is>
           <t>SKU-BEF4345E20C9</t>
         </is>
@@ -2857,7 +2922,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3006,7 +3071,7 @@
         </is>
       </c>
       <c r="AO14" s="1" t="n">
-        <v>45183.4665625</v>
+        <v>25569.12552295139</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
@@ -3019,6 +3084,11 @@
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
+        <is>
+          <t>Debrex</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
         <is>
           <t>SKU-698455570BC8</t>
         </is>
@@ -3039,7 +3109,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3207,6 +3277,11 @@
         </is>
       </c>
       <c r="AT15" t="inlineStr">
+        <is>
+          <t>Debrex</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
         <is>
           <t>SKU-E594F939D567</t>
         </is>
@@ -3227,7 +3302,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3391,6 +3466,11 @@
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
+        <is>
+          <t>Debrex</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
         <is>
           <t>SKU-0F054783CEDD</t>
         </is>
@@ -3411,7 +3491,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3560,7 +3640,7 @@
         </is>
       </c>
       <c r="AO17" s="1" t="n">
-        <v>45812.49896990741</v>
+        <v>25569.12553023148</v>
       </c>
       <c r="AP17" t="n">
         <v>0</v>
@@ -3581,6 +3661,11 @@
         </is>
       </c>
       <c r="AT17" t="inlineStr">
+        <is>
+          <t>CIBINQO</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
         <is>
           <t>SKU-6C9C78E7E652</t>
         </is>
@@ -3601,7 +3686,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3758,7 +3843,7 @@
         </is>
       </c>
       <c r="AO18" s="1" t="n">
-        <v>45812.49886574074</v>
+        <v>25569.12553023148</v>
       </c>
       <c r="AP18" t="n">
         <v>0</v>
@@ -3775,6 +3860,11 @@
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
+        <is>
+          <t>CIBINQO</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
         <is>
           <t>SKU-4E49636AE421</t>
         </is>
@@ -3795,7 +3885,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3952,7 +4042,7 @@
         </is>
       </c>
       <c r="AO19" s="1" t="n">
-        <v>45812.49875</v>
+        <v>25569.12553023148</v>
       </c>
       <c r="AP19" t="n">
         <v>0</v>
@@ -3969,6 +4059,11 @@
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
+        <is>
+          <t>CIBINQO</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
         <is>
           <t>SKU-A1C384F01772</t>
         </is>
@@ -3989,7 +4084,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4145,6 +4240,11 @@
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
+        <is>
+          <t>Fenofibrate Ethypharm</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
         <is>
           <t>SKU-2B63EB4F6D11</t>
         </is>
@@ -4165,7 +4265,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4308,7 +4408,7 @@
         </is>
       </c>
       <c r="AO21" s="1" t="n">
-        <v>45511.3684375</v>
+        <v>25569.12552674768</v>
       </c>
       <c r="AP21" t="n">
         <v>0</v>
@@ -4329,6 +4429,11 @@
         </is>
       </c>
       <c r="AT21" t="inlineStr">
+        <is>
+          <t>Lenvatinib BOS</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
         <is>
           <t>SKU-F81C3D558095</t>
         </is>
@@ -4349,7 +4454,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4496,7 +4601,7 @@
         </is>
       </c>
       <c r="AO22" s="1" t="n">
-        <v>45697.40587962963</v>
+        <v>25569.12552890046</v>
       </c>
       <c r="AP22" t="n">
         <v>390</v>
@@ -4513,6 +4618,11 @@
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
+        <is>
+          <t>Hulio</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
         <is>
           <t>SKU-AE2AC77A63FC</t>
         </is>
@@ -4533,7 +4643,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4680,7 +4790,7 @@
         </is>
       </c>
       <c r="AO23" s="1" t="n">
-        <v>45697.40568287037</v>
+        <v>25569.12552890046</v>
       </c>
       <c r="AP23" t="n">
         <v>0</v>
@@ -4697,6 +4807,11 @@
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
+        <is>
+          <t>Hulio</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
         <is>
           <t>SKU-A35835D40204</t>
         </is>
@@ -4717,7 +4832,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4862,7 +4977,7 @@
         </is>
       </c>
       <c r="AO24" s="1" t="n">
-        <v>45769.70961805555</v>
+        <v>25569.1255297338</v>
       </c>
       <c r="AP24" t="n">
         <v>0</v>
@@ -4883,6 +4998,11 @@
         </is>
       </c>
       <c r="AT24" t="inlineStr">
+        <is>
+          <t>Nicorette Freshmint Gum</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
         <is>
           <t>SKU-6EC4B38EE6D5</t>
         </is>
@@ -4903,7 +5023,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5048,7 +5168,7 @@
         </is>
       </c>
       <c r="AO25" s="1" t="n">
-        <v>45769.70938657408</v>
+        <v>25569.1255297338</v>
       </c>
       <c r="AP25" t="n">
         <v>0</v>
@@ -5065,6 +5185,11 @@
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
+        <is>
+          <t>Nicorette Freshmint Gum</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
         <is>
           <t>SKU-CCB47B2B37F6</t>
         </is>
@@ -5085,7 +5210,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5230,7 +5355,7 @@
         </is>
       </c>
       <c r="AO26" s="1" t="n">
-        <v>45673.37880787037</v>
+        <v>25569.12552862268</v>
       </c>
       <c r="AP26" t="n">
         <v>0</v>
@@ -5251,6 +5376,11 @@
         </is>
       </c>
       <c r="AT26" t="inlineStr">
+        <is>
+          <t>Adacter</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
         <is>
           <t>SKU-D7823DA89BA0</t>
         </is>
@@ -5271,7 +5401,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5435,6 +5565,11 @@
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
+        <is>
+          <t>Debrex</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
         <is>
           <t>SKU-B2D5CF859437</t>
         </is>
@@ -5455,7 +5590,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5615,6 +5750,11 @@
         </is>
       </c>
       <c r="AT28" t="inlineStr">
+        <is>
+          <t>Inogara</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
         <is>
           <t>SKU-151E04D13223</t>
         </is>
@@ -5635,7 +5775,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5778,7 +5918,7 @@
         </is>
       </c>
       <c r="AO29" s="1" t="n">
-        <v>45812.48840277778</v>
+        <v>25569.12553023148</v>
       </c>
       <c r="AP29" t="n">
         <v>136.2949981689453</v>
@@ -5799,6 +5939,11 @@
         </is>
       </c>
       <c r="AT29" t="inlineStr">
+        <is>
+          <t>Apilipx</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
         <is>
           <t>SKU-54B801EA6633</t>
         </is>
@@ -5819,7 +5964,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5962,7 +6107,7 @@
         </is>
       </c>
       <c r="AO30" s="1" t="n">
-        <v>45812.48813657407</v>
+        <v>25569.12553023148</v>
       </c>
       <c r="AP30" t="n">
         <v>0</v>
@@ -5983,6 +6128,11 @@
         </is>
       </c>
       <c r="AT30" t="inlineStr">
+        <is>
+          <t>Apilipx</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
         <is>
           <t>SKU-BBBB3B7DC681</t>
         </is>
@@ -6003,7 +6153,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6146,7 +6296,7 @@
         </is>
       </c>
       <c r="AO31" s="1" t="n">
-        <v>45812.48796296296</v>
+        <v>25569.12553023148</v>
       </c>
       <c r="AP31" t="n">
         <v>169.3470001220703</v>
@@ -6159,6 +6309,11 @@
       <c r="AR31" t="inlineStr"/>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
+        <is>
+          <t>Apilipx</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
         <is>
           <t>SKU-8B39B0905DE9</t>
         </is>
@@ -6179,7 +6334,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6322,7 +6477,7 @@
         </is>
       </c>
       <c r="AO32" s="1" t="n">
-        <v>45812.4877662037</v>
+        <v>25569.12553023148</v>
       </c>
       <c r="AP32" t="n">
         <v>0</v>
@@ -6339,6 +6494,11 @@
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
+        <is>
+          <t>Apilipx</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
         <is>
           <t>SKU-C12B0D8D181F</t>
         </is>
@@ -6359,7 +6519,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6508,7 +6668,7 @@
         </is>
       </c>
       <c r="AO33" s="1" t="n">
-        <v>45722.51515046296</v>
+        <v>25569.12552918982</v>
       </c>
       <c r="AP33" t="n">
         <v>0</v>
@@ -6521,6 +6681,11 @@
       <c r="AR33" t="inlineStr"/>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clodipan 8 mg and 5mg </t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
         <is>
           <t>SKU-1E7C8A1E783F</t>
         </is>
@@ -6541,7 +6706,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6690,7 +6855,7 @@
         </is>
       </c>
       <c r="AO34" s="1" t="n">
-        <v>45722.51556712963</v>
+        <v>25569.12552918982</v>
       </c>
       <c r="AP34" t="n">
         <v>0</v>
@@ -6711,6 +6876,11 @@
         </is>
       </c>
       <c r="AT34" t="inlineStr">
+        <is>
+          <t>Clodipan 16 mg and 5 mg</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
         <is>
           <t>SKU-26AD418C42A8</t>
         </is>
@@ -6731,7 +6901,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6872,7 +7042,7 @@
         </is>
       </c>
       <c r="AO35" s="1" t="n">
-        <v>45183.55121527778</v>
+        <v>25569.12552295139</v>
       </c>
       <c r="AP35" t="n">
         <v>0</v>
@@ -6885,6 +7055,11 @@
       <c r="AR35" t="inlineStr"/>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
+        <is>
+          <t>AMLOCARD 10 mg tablets</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
         <is>
           <t>SKU-DE6B50F2FAF8</t>
         </is>
@@ -6905,7 +7080,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7057,6 +7232,11 @@
       <c r="AR36" t="inlineStr"/>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
+        <is>
+          <t>Cekea</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
         <is>
           <t>SKU-D6544A0EA73D</t>
         </is>
@@ -7077,7 +7257,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7226,7 +7406,7 @@
         </is>
       </c>
       <c r="AO37" s="1" t="n">
-        <v>45221.58234953704</v>
+        <v>25569.12552339121</v>
       </c>
       <c r="AP37" t="n">
         <v>0</v>
@@ -7247,6 +7427,11 @@
         </is>
       </c>
       <c r="AT37" t="inlineStr">
+        <is>
+          <t>Lumify</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
         <is>
           <t>SKU-C29D255DD0BE</t>
         </is>
@@ -7267,7 +7452,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7408,7 +7593,7 @@
         </is>
       </c>
       <c r="AO38" s="1" t="n">
-        <v>45362.57755787037</v>
+        <v>25569.12552502315</v>
       </c>
       <c r="AP38" t="n">
         <v>0</v>
@@ -7425,6 +7610,11 @@
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
+        <is>
+          <t>Welireg</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
         <is>
           <t>SKU-0BA2B20998BF</t>
         </is>
@@ -7445,7 +7635,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7598,7 +7788,7 @@
         </is>
       </c>
       <c r="AO39" s="1" t="n">
-        <v>45221.39807870371</v>
+        <v>25569.12552339121</v>
       </c>
       <c r="AP39" t="n">
         <v>75</v>
@@ -7619,6 +7809,11 @@
         </is>
       </c>
       <c r="AT39" t="inlineStr">
+        <is>
+          <t>Lomipat</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
         <is>
           <t>SKU-3A5354F79B0B</t>
         </is>
@@ -7639,7 +7834,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7792,7 +7987,7 @@
         </is>
       </c>
       <c r="AO40" s="1" t="n">
-        <v>45221.39798611111</v>
+        <v>25569.12552339121</v>
       </c>
       <c r="AP40" t="n">
         <v>60</v>
@@ -7805,6 +8000,11 @@
       <c r="AR40" t="inlineStr"/>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
+        <is>
+          <t>Lomipat</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
         <is>
           <t>SKU-28C5F93BED16</t>
         </is>
@@ -7825,7 +8025,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -7978,7 +8178,7 @@
         </is>
       </c>
       <c r="AO41" s="1" t="n">
-        <v>45221.39790509259</v>
+        <v>25569.12552339121</v>
       </c>
       <c r="AP41" t="n">
         <v>36</v>
@@ -7999,6 +8199,11 @@
         </is>
       </c>
       <c r="AT41" t="inlineStr">
+        <is>
+          <t>Lomipat</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
         <is>
           <t>SKU-DC059EBD290B</t>
         </is>
@@ -8019,7 +8224,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8172,7 +8377,7 @@
         </is>
       </c>
       <c r="AO42" s="1" t="n">
-        <v>45221.39780092592</v>
+        <v>25569.12552339121</v>
       </c>
       <c r="AP42" t="n">
         <v>31.5</v>
@@ -8193,6 +8398,11 @@
         </is>
       </c>
       <c r="AT42" t="inlineStr">
+        <is>
+          <t>Lomipat</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
         <is>
           <t>SKU-EF2FE6C6B81F</t>
         </is>
@@ -8213,7 +8423,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8381,6 +8591,11 @@
         </is>
       </c>
       <c r="AT43" t="inlineStr">
+        <is>
+          <t>Ursofalk</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
         <is>
           <t>SKU-4BBA3A119D82</t>
         </is>
@@ -8401,7 +8616,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8558,7 +8773,7 @@
         </is>
       </c>
       <c r="AO44" s="1" t="n">
-        <v>45202.38087962963</v>
+        <v>25569.1255231713</v>
       </c>
       <c r="AP44" t="n">
         <v>25.57500076293945</v>
@@ -8571,6 +8786,11 @@
       <c r="AR44" t="inlineStr"/>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
+        <is>
+          <t>Movicol Paediatric Plain</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
         <is>
           <t>SKU-E02F9AB7C167</t>
         </is>
@@ -8591,7 +8811,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8738,7 +8958,7 @@
         </is>
       </c>
       <c r="AO45" s="1" t="n">
-        <v>45362.49284722222</v>
+        <v>25569.12552502315</v>
       </c>
       <c r="AP45" t="n">
         <v>0</v>
@@ -8755,6 +8975,11 @@
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
+        <is>
+          <t>Pelgraz 6 mg in 0.6 ml</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
         <is>
           <t>SKU-6F115D7F19E6</t>
         </is>
@@ -8775,7 +9000,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8920,7 +9145,7 @@
         </is>
       </c>
       <c r="AO46" s="1" t="n">
-        <v>45221.39893518519</v>
+        <v>25569.12552339121</v>
       </c>
       <c r="AP46" t="n">
         <v>0</v>
@@ -8941,6 +9166,11 @@
         </is>
       </c>
       <c r="AT46" t="inlineStr">
+        <is>
+          <t>Pantrox</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
         <is>
           <t>SKU-C548BEA75854</t>
         </is>
@@ -8961,7 +9191,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9106,7 +9336,7 @@
         </is>
       </c>
       <c r="AO47" s="1" t="n">
-        <v>45221.39884259259</v>
+        <v>25569.12552339121</v>
       </c>
       <c r="AP47" t="n">
         <v>0</v>
@@ -9127,6 +9357,11 @@
         </is>
       </c>
       <c r="AT47" t="inlineStr">
+        <is>
+          <t>Pantrox</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
         <is>
           <t>SKU-E9F686004E0D</t>
         </is>
@@ -9147,7 +9382,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9292,7 +9527,7 @@
         </is>
       </c>
       <c r="AO48" s="1" t="n">
-        <v>45221.39875</v>
+        <v>25569.12552339121</v>
       </c>
       <c r="AP48" t="n">
         <v>0</v>
@@ -9309,6 +9544,11 @@
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
+        <is>
+          <t>Pantrox</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
         <is>
           <t>SKU-BC0B96AE5D59</t>
         </is>
@@ -9329,7 +9569,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9474,7 +9714,7 @@
         </is>
       </c>
       <c r="AO49" s="1" t="n">
-        <v>45350.39679398148</v>
+        <v>25569.12552488426</v>
       </c>
       <c r="AP49" t="n">
         <v>0</v>
@@ -9495,6 +9735,11 @@
         </is>
       </c>
       <c r="AT49" t="inlineStr">
+        <is>
+          <t>Triplixam</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
         <is>
           <t>SKU-4A00E521EFD1</t>
         </is>
@@ -9515,7 +9760,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9660,7 +9905,7 @@
         </is>
       </c>
       <c r="AO50" s="1" t="n">
-        <v>45350.3965625</v>
+        <v>25569.12552488426</v>
       </c>
       <c r="AP50" t="n">
         <v>0</v>
@@ -9677,6 +9922,11 @@
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
+        <is>
+          <t>Triplixam</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
         <is>
           <t>SKU-E537D59EB4FC</t>
         </is>
@@ -9697,7 +9947,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9842,7 +10092,7 @@
         </is>
       </c>
       <c r="AO51" s="1" t="n">
-        <v>45350.39635416667</v>
+        <v>25569.12552488426</v>
       </c>
       <c r="AP51" t="n">
         <v>0</v>
@@ -9859,6 +10109,11 @@
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
+        <is>
+          <t>Triplixam</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
         <is>
           <t>SKU-506B593445D9</t>
         </is>
@@ -9879,7 +10134,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10024,7 +10279,7 @@
         </is>
       </c>
       <c r="AO52" s="1" t="n">
-        <v>45350.39619212963</v>
+        <v>25569.12552488426</v>
       </c>
       <c r="AP52" t="n">
         <v>0</v>
@@ -10041,6 +10296,11 @@
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
+        <is>
+          <t>Triplixam</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
         <is>
           <t>SKU-27235B3FBDED</t>
         </is>
@@ -10061,7 +10321,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10221,6 +10481,11 @@
         </is>
       </c>
       <c r="AT53" t="inlineStr">
+        <is>
+          <t>Tadalafil EVA</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
         <is>
           <t>SKU-DA976A379631</t>
         </is>
@@ -10241,7 +10506,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10386,7 +10651,7 @@
         </is>
       </c>
       <c r="AO54" s="1" t="n">
-        <v>45655.32273148148</v>
+        <v>25569.12552841435</v>
       </c>
       <c r="AP54" t="n">
         <v>42.47880172729492</v>
@@ -10407,6 +10672,11 @@
         </is>
       </c>
       <c r="AT54" t="inlineStr">
+        <is>
+          <t>Nevotic</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
         <is>
           <t>SKU-AD6B754836A1</t>
         </is>
@@ -10427,7 +10697,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10572,7 +10842,7 @@
         </is>
       </c>
       <c r="AO55" s="1" t="n">
-        <v>45741.68148148148</v>
+        <v>25569.12552940972</v>
       </c>
       <c r="AP55" t="n">
         <v>0</v>
@@ -10593,6 +10863,11 @@
         </is>
       </c>
       <c r="AT55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nexium 10 mg </t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
         <is>
           <t>SKU-0D8FFE58CD55</t>
         </is>
@@ -10613,7 +10888,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10766,7 +11041,7 @@
         </is>
       </c>
       <c r="AO56" s="1" t="n">
-        <v>45222.56365740741</v>
+        <v>25569.12552340278</v>
       </c>
       <c r="AP56" t="n">
         <v>0</v>
@@ -10783,6 +11058,11 @@
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tezspire 210 mg per 1.9 ml pen </t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
         <is>
           <t>SKU-31459261B7B0</t>
         </is>
@@ -10803,7 +11083,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -10967,6 +11247,11 @@
         </is>
       </c>
       <c r="AT57" t="inlineStr">
+        <is>
+          <t>Tiomist</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
         <is>
           <t>SKU-0B990D5BE959</t>
         </is>
@@ -10987,7 +11272,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11147,6 +11432,11 @@
         </is>
       </c>
       <c r="AT58" t="inlineStr">
+        <is>
+          <t>Paxas</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
         <is>
           <t>SKU-DF9B65D0B9C3</t>
         </is>
@@ -11167,7 +11457,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11323,6 +11613,11 @@
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
+        <is>
+          <t>Paxas</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
         <is>
           <t>SKU-BBF377B09E9C</t>
         </is>
@@ -11343,7 +11638,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11503,6 +11798,11 @@
         </is>
       </c>
       <c r="AT60" t="inlineStr">
+        <is>
+          <t>Paxas</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
         <is>
           <t>SKU-955882909B80</t>
         </is>
@@ -11523,7 +11823,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11683,6 +11983,11 @@
         </is>
       </c>
       <c r="AT61" t="inlineStr">
+        <is>
+          <t>Daroxime</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
         <is>
           <t>SKU-05760B047622</t>
         </is>
@@ -11703,7 +12008,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -11850,7 +12155,7 @@
         </is>
       </c>
       <c r="AO62" s="1" t="n">
-        <v>45832.57883101852</v>
+        <v>25569.12553046296</v>
       </c>
       <c r="AP62" t="n">
         <v>0</v>
@@ -11871,6 +12176,11 @@
         </is>
       </c>
       <c r="AT62" t="inlineStr">
+        <is>
+          <t>Enoxaparin BOS</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
         <is>
           <t>SKU-0869474D3CDE</t>
         </is>
@@ -11891,7 +12201,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12038,7 +12348,7 @@
         </is>
       </c>
       <c r="AO63" s="1" t="n">
-        <v>45832.57940972222</v>
+        <v>25569.12553046296</v>
       </c>
       <c r="AP63" t="n">
         <v>0</v>
@@ -12055,6 +12365,11 @@
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
+        <is>
+          <t>Enoxaparin BOS</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
         <is>
           <t>SKU-C8BBCAB467D2</t>
         </is>
@@ -12075,7 +12390,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12222,7 +12537,7 @@
         </is>
       </c>
       <c r="AO64" s="1" t="n">
-        <v>45832.57940972222</v>
+        <v>25569.12553046296</v>
       </c>
       <c r="AP64" t="n">
         <v>0</v>
@@ -12239,6 +12554,11 @@
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
+        <is>
+          <t>Enoxaparin BOS</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
         <is>
           <t>SKU-9E706FE71603</t>
         </is>
@@ -12259,7 +12579,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12406,7 +12726,7 @@
         </is>
       </c>
       <c r="AO65" s="1" t="n">
-        <v>45832.57998842592</v>
+        <v>25569.12553046296</v>
       </c>
       <c r="AP65" t="n">
         <v>0</v>
@@ -12423,6 +12743,11 @@
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
+        <is>
+          <t>Enoxaparin BOS</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
         <is>
           <t>SKU-6D2EEA3A2B0B</t>
         </is>
@@ -12443,7 +12768,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12592,7 +12917,7 @@
         </is>
       </c>
       <c r="AO66" s="1" t="n">
-        <v>45378.62862268519</v>
+        <v>25569.12552520833</v>
       </c>
       <c r="AP66" t="n">
         <v>0</v>
@@ -12613,6 +12938,11 @@
         </is>
       </c>
       <c r="AT66" t="inlineStr">
+        <is>
+          <t>Sineo</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
         <is>
           <t>SKU-5FAC69706110</t>
         </is>
@@ -12633,7 +12963,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12784,7 +13114,7 @@
         </is>
       </c>
       <c r="AO67" s="1" t="n">
-        <v>45511.36516203704</v>
+        <v>25569.12552674768</v>
       </c>
       <c r="AP67" t="n">
         <v>0</v>
@@ -12801,6 +13131,11 @@
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
+        <is>
+          <t>Celezon</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
         <is>
           <t>SKU-4B33B7018B22</t>
         </is>
@@ -12821,7 +13156,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -12989,6 +13324,11 @@
         </is>
       </c>
       <c r="AT68" t="inlineStr">
+        <is>
+          <t>CIDOCOMB</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
         <is>
           <t>SKU-881C699FFF4F</t>
         </is>
@@ -13009,7 +13349,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13150,7 +13490,7 @@
         </is>
       </c>
       <c r="AO69" s="1" t="n">
-        <v>45236.5922337963</v>
+        <v>25569.12552356481</v>
       </c>
       <c r="AP69" t="n">
         <v>0</v>
@@ -13171,6 +13511,11 @@
         </is>
       </c>
       <c r="AT69" t="inlineStr">
+        <is>
+          <t>Onstera</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
         <is>
           <t>SKU-E36205F7CC5F</t>
         </is>
@@ -13191,7 +13536,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13351,6 +13696,11 @@
         </is>
       </c>
       <c r="AT70" t="inlineStr">
+        <is>
+          <t>Verotec</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
         <is>
           <t>SKU-043069D6F2B2</t>
         </is>
@@ -13371,7 +13721,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13531,6 +13881,11 @@
         </is>
       </c>
       <c r="AT71" t="inlineStr">
+        <is>
+          <t>Verotec</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
         <is>
           <t>SKU-445FE88E141C</t>
         </is>
@@ -13551,7 +13906,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13711,6 +14066,11 @@
         </is>
       </c>
       <c r="AT72" t="inlineStr">
+        <is>
+          <t>Verotec</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
         <is>
           <t>SKU-1AAF46385E4B</t>
         </is>
@@ -13731,7 +14091,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -13876,7 +14236,7 @@
         </is>
       </c>
       <c r="AO73" s="1" t="n">
-        <v>45238.66215277778</v>
+        <v>25569.12552358796</v>
       </c>
       <c r="AP73" t="n">
         <v>0</v>
@@ -13893,6 +14253,11 @@
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
+        <is>
+          <t>Ranexa</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
         <is>
           <t>SKU-D7AD9ED2E283</t>
         </is>
@@ -13913,7 +14278,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14073,6 +14438,11 @@
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
+        <is>
+          <t>Ranexa</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
         <is>
           <t>SKU-BBFBB558A6EA</t>
         </is>
@@ -14093,7 +14463,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14257,6 +14627,11 @@
         </is>
       </c>
       <c r="AT75" t="inlineStr">
+        <is>
+          <t>Ranexa</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
         <is>
           <t>SKU-700727ED536D</t>
         </is>
@@ -14277,7 +14652,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14430,7 +14805,7 @@
         </is>
       </c>
       <c r="AO76" s="1" t="n">
-        <v>45767.59581018519</v>
+        <v>25569.12552971065</v>
       </c>
       <c r="AP76" t="n">
         <v>0</v>
@@ -14447,6 +14822,11 @@
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
+        <is>
+          <t>Diafor XR</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
         <is>
           <t>SKU-B43215E58E49</t>
         </is>
@@ -14467,7 +14847,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14620,7 +15000,7 @@
         </is>
       </c>
       <c r="AO77" s="1" t="n">
-        <v>45767.59603009259</v>
+        <v>25569.12552971065</v>
       </c>
       <c r="AP77" t="n">
         <v>0</v>
@@ -14637,6 +15017,11 @@
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
+        <is>
+          <t>Diafor XR</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
         <is>
           <t>SKU-DF1C9C3D2BCE</t>
         </is>
@@ -14657,7 +15042,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -14810,7 +15195,7 @@
         </is>
       </c>
       <c r="AO78" s="1" t="n">
-        <v>45777.56741898148</v>
+        <v>25569.12552982639</v>
       </c>
       <c r="AP78" t="n">
         <v>0</v>
@@ -14827,6 +15212,11 @@
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
+        <is>
+          <t>Diafor XR</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
         <is>
           <t>SKU-89E93DE895D9</t>
         </is>
@@ -14847,7 +15237,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15000,7 +15390,7 @@
         </is>
       </c>
       <c r="AO79" s="1" t="n">
-        <v>45767.59622685185</v>
+        <v>25569.12552971065</v>
       </c>
       <c r="AP79" t="n">
         <v>0</v>
@@ -15021,6 +15411,11 @@
         </is>
       </c>
       <c r="AT79" t="inlineStr">
+        <is>
+          <t>Diafor XR</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
         <is>
           <t>SKU-C72AA40357B4</t>
         </is>
@@ -15041,7 +15436,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15194,7 +15589,7 @@
         </is>
       </c>
       <c r="AO80" s="1" t="n">
-        <v>45767.59644675926</v>
+        <v>25569.12552971065</v>
       </c>
       <c r="AP80" t="n">
         <v>0</v>
@@ -15215,6 +15610,11 @@
         </is>
       </c>
       <c r="AT80" t="inlineStr">
+        <is>
+          <t>Diafor XR</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
         <is>
           <t>SKU-C90752B70506</t>
         </is>
@@ -15235,7 +15635,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15388,7 +15788,7 @@
         </is>
       </c>
       <c r="AO81" s="1" t="n">
-        <v>45257.54685185185</v>
+        <v>25569.12552380787</v>
       </c>
       <c r="AP81" t="n">
         <v>0</v>
@@ -15405,6 +15805,11 @@
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
+        <is>
+          <t>Diafor XR</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
         <is>
           <t>SKU-4017DA352298</t>
         </is>
@@ -15425,7 +15830,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15578,7 +15983,7 @@
         </is>
       </c>
       <c r="AO82" s="1" t="n">
-        <v>45257.54770833333</v>
+        <v>25569.12552380787</v>
       </c>
       <c r="AP82" t="n">
         <v>0</v>
@@ -15595,6 +16000,11 @@
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
+        <is>
+          <t>Allocar</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
         <is>
           <t>SKU-E255F90783E0</t>
         </is>
@@ -15615,7 +16025,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -15768,7 +16178,7 @@
         </is>
       </c>
       <c r="AO83" s="1" t="n">
-        <v>45257.54761574074</v>
+        <v>25569.12552380787</v>
       </c>
       <c r="AP83" t="n">
         <v>0</v>
@@ -15785,6 +16195,11 @@
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
+        <is>
+          <t>Allocar</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
         <is>
           <t>SKU-49D6D2001297</t>
         </is>
@@ -15805,7 +16220,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -15950,7 +16365,7 @@
         </is>
       </c>
       <c r="AO84" s="1" t="n">
-        <v>45257.54850694445</v>
+        <v>25569.12552380787</v>
       </c>
       <c r="AP84" t="n">
         <v>0</v>
@@ -15971,6 +16386,11 @@
         </is>
       </c>
       <c r="AT84" t="inlineStr">
+        <is>
+          <t>Lertiv</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
         <is>
           <t>SKU-CEB151A97684</t>
         </is>
@@ -15991,7 +16411,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16136,7 +16556,7 @@
         </is>
       </c>
       <c r="AO85" s="1" t="n">
-        <v>45257.54842592592</v>
+        <v>25569.12552380787</v>
       </c>
       <c r="AP85" t="n">
         <v>0</v>
@@ -16157,6 +16577,11 @@
         </is>
       </c>
       <c r="AT85" t="inlineStr">
+        <is>
+          <t>Lertiv</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
         <is>
           <t>SKU-1A7E32E49E96</t>
         </is>
@@ -16177,7 +16602,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16330,7 +16755,7 @@
         </is>
       </c>
       <c r="AO86" s="1" t="n">
-        <v>45257.54833333333</v>
+        <v>25569.12552380787</v>
       </c>
       <c r="AP86" t="n">
         <v>0</v>
@@ -16347,6 +16772,11 @@
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
+        <is>
+          <t>Lertiv</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
         <is>
           <t>SKU-84C0BFED9682</t>
         </is>
@@ -16367,7 +16797,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16520,7 +16950,7 @@
         </is>
       </c>
       <c r="AO87" s="1" t="n">
-        <v>45257.54824074074</v>
+        <v>25569.12552380787</v>
       </c>
       <c r="AP87" t="n">
         <v>30</v>
@@ -16537,6 +16967,11 @@
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
+        <is>
+          <t>Lertiv</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
         <is>
           <t>SKU-BA8E8B9751CE</t>
         </is>
@@ -16557,7 +16992,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16702,7 +17137,7 @@
         </is>
       </c>
       <c r="AO88" s="1" t="n">
-        <v>45349.60936342592</v>
+        <v>25569.12552487268</v>
       </c>
       <c r="AP88" t="n">
         <v>0</v>
@@ -16719,6 +17154,11 @@
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
+        <is>
+          <t>GONAL-f 150 IU per 0.25 ml</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
         <is>
           <t>SKU-22FB4BC1C2D8</t>
         </is>
@@ -16739,7 +17179,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -16880,7 +17320,7 @@
         </is>
       </c>
       <c r="AO89" s="1" t="n">
-        <v>45264.44614583333</v>
+        <v>25569.12552388889</v>
       </c>
       <c r="AP89" t="n">
         <v>0</v>
@@ -16897,6 +17337,11 @@
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
+        <is>
+          <t>Pantrox</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
         <is>
           <t>SKU-92DF773636E6</t>
         </is>
@@ -16917,7 +17362,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17060,7 +17505,7 @@
         </is>
       </c>
       <c r="AO90" s="1" t="n">
-        <v>45265.4264699074</v>
+        <v>25569.12552390046</v>
       </c>
       <c r="AP90" t="n">
         <v>0</v>
@@ -17081,6 +17526,11 @@
         </is>
       </c>
       <c r="AT90" t="inlineStr">
+        <is>
+          <t>Pafazin</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
         <is>
           <t>SKU-A8858D87029D</t>
         </is>
@@ -17101,7 +17551,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17259,6 +17709,11 @@
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
+        <is>
+          <t>Pafazin</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
         <is>
           <t>SKU-03C6139722BF</t>
         </is>
@@ -17279,7 +17734,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17420,7 +17875,7 @@
         </is>
       </c>
       <c r="AO92" s="1" t="n">
-        <v>45271.43811342592</v>
+        <v>25569.12552396991</v>
       </c>
       <c r="AP92" t="n">
         <v>0</v>
@@ -17437,6 +17892,11 @@
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
+        <is>
+          <t>Zodinex</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
         <is>
           <t>SKU-6B426E0C0EC9</t>
         </is>
@@ -17457,7 +17917,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17625,6 +18085,11 @@
         </is>
       </c>
       <c r="AT93" t="inlineStr">
+        <is>
+          <t>Azebat</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
         <is>
           <t>SKU-A8228338258C</t>
         </is>
@@ -17645,7 +18110,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -17790,7 +18255,7 @@
         </is>
       </c>
       <c r="AO94" s="1" t="n">
-        <v>45273.56574074074</v>
+        <v>25569.12552399305</v>
       </c>
       <c r="AP94" t="n">
         <v>0</v>
@@ -17807,6 +18272,11 @@
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
+        <is>
+          <t>Pliaglis 15 gram Cream</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
         <is>
           <t>SKU-40C0E1D4AB9C</t>
         </is>
@@ -17827,7 +18297,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -17972,7 +18442,7 @@
         </is>
       </c>
       <c r="AO95" s="1" t="n">
-        <v>45273.59413194445</v>
+        <v>25569.12552399305</v>
       </c>
       <c r="AP95" t="n">
         <v>0</v>
@@ -17993,6 +18463,11 @@
         </is>
       </c>
       <c r="AT95" t="inlineStr">
+        <is>
+          <t>Pliaglis 30 gram Cream</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
         <is>
           <t>SKU-CF9A17DA242C</t>
         </is>
@@ -18013,7 +18488,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18177,6 +18652,11 @@
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
+        <is>
+          <t>Cekea</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
         <is>
           <t>SKU-D2AA56D247DB</t>
         </is>
@@ -18197,7 +18677,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18338,7 +18818,7 @@
         </is>
       </c>
       <c r="AO97" s="1" t="n">
-        <v>45481.46737268518</v>
+        <v>25569.12552640046</v>
       </c>
       <c r="AP97" t="n">
         <v>0</v>
@@ -18355,6 +18835,11 @@
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
+        <is>
+          <t>Donifoxate</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
         <is>
           <t>SKU-0CEBA852D4F1</t>
         </is>
@@ -18375,7 +18860,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18518,7 +19003,7 @@
         </is>
       </c>
       <c r="AO98" s="1" t="n">
-        <v>45279.46821759259</v>
+        <v>25569.1255240625</v>
       </c>
       <c r="AP98" t="n">
         <v>0</v>
@@ -18535,6 +19020,11 @@
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
+        <is>
+          <t>LERHASA</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
         <is>
           <t>SKU-CEA95BFEE8EE</t>
         </is>
@@ -18555,7 +19045,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -18715,6 +19205,11 @@
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
+        <is>
+          <t>Zeposia</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
         <is>
           <t>SKU-5630B256EE17</t>
         </is>
@@ -18735,7 +19230,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -18899,6 +19394,11 @@
         </is>
       </c>
       <c r="AT100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zeposia (initiation pack) 4 caps 0.23 mg and 3 caps 0.46 mg </t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
         <is>
           <t>SKU-7F632831C8CA</t>
         </is>
@@ -18919,7 +19419,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19060,7 +19560,7 @@
         </is>
       </c>
       <c r="AO101" s="1" t="n">
-        <v>45617.42061342593</v>
+        <v>25569.12552797454</v>
       </c>
       <c r="AP101" t="n">
         <v>0</v>
@@ -19073,6 +19573,11 @@
       <c r="AR101" t="inlineStr"/>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>Esqua</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-0C7E499BCE7C</t>
         </is>
@@ -19089,7 +19594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19135,100 +19640,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19260,7 +19770,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19275,92 +19785,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-66054</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>356.71</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>530</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19392,7 +19907,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19407,92 +19922,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-85068</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>390.92</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>531</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19524,7 +20044,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19539,92 +20059,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-52991</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>186.17</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>532</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19656,7 +20181,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19671,92 +20196,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-13738</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>119.4</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>533</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19788,7 +20318,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -19803,92 +20333,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-91289</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>150.73</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>534</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19920,7 +20455,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -19935,92 +20470,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-64146</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>461.61</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Thermometer</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>535</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20052,7 +20592,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20067,92 +20607,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-38521</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>273.64</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Thermometer</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>536</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20184,7 +20729,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20199,92 +20744,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-74097</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>24.51</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>537</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20316,7 +20866,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20331,92 +20881,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-86782</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>23.5</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>538</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20448,7 +21003,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20463,92 +21018,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-28996</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>452.15</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>539</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20580,7 +21140,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20595,92 +21155,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-47950</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>484.73</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>540</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20697,7 +21262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20803,6 +21368,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -20838,7 +21413,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -20903,6 +21478,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-A916868F0F8D</t>
         </is>
@@ -20939,7 +21524,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21004,6 +21589,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-FA2CF3107700</t>
         </is>
@@ -21040,7 +21635,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21105,6 +21700,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-371E51D68655</t>
         </is>
@@ -21141,7 +21746,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21206,6 +21811,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-397FC4AC7964</t>
         </is>
@@ -21242,7 +21857,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21307,6 +21922,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-272501DB813A</t>
         </is>
@@ -21343,7 +21968,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21408,6 +22033,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-3C4CE9948E62</t>
         </is>
@@ -21444,7 +22079,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21509,6 +22144,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-A1F8F0539802</t>
         </is>
@@ -21545,7 +22190,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21610,6 +22255,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-C14BE86D7975</t>
         </is>
@@ -21646,7 +22301,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -21711,6 +22366,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-67CA6B0AFC6C</t>
         </is>
@@ -21747,7 +22412,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -21812,6 +22477,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-E1AF077774E1</t>
         </is>
@@ -21848,7 +22523,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -21913,6 +22588,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-260FF45EB9B9</t>
         </is>
@@ -21949,7 +22634,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22014,6 +22699,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-38CA5EE42525</t>
         </is>
@@ -22050,7 +22745,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22115,6 +22810,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-DB835FA7AFB0</t>
         </is>
@@ -22151,7 +22856,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22216,6 +22921,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-F900AFBDC2B9</t>
         </is>
@@ -22252,7 +22967,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22317,6 +23032,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-D9B3452AFCC0</t>
         </is>
@@ -22353,7 +23078,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22418,6 +23143,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-F906AEDB8F6C</t>
         </is>
@@ -22454,7 +23189,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22519,6 +23254,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-029B56BE550F</t>
         </is>
@@ -22555,7 +23300,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22620,6 +23365,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-E99048D089B8</t>
         </is>
@@ -22656,7 +23411,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -22721,6 +23476,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-D37CB09A359E</t>
         </is>
@@ -22757,7 +23522,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -22822,6 +23587,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-F223EB776CAD</t>
         </is>

--- a/product_upload/packages/54/file.xlsx
+++ b/product_upload/packages/54/file.xlsx
@@ -682,8 +682,16 @@
           <t>8882333351-630-462571762801</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Amlohope Plus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Amlohope Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -869,8 +877,16 @@
           <t>5639714113-597-565999233015</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Amlohope Plus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Amlohope Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1623,8 +1639,16 @@
           <t>7426691585-192-577292502997</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALUNBRIG</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ALUNBRIG detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1814,8 +1838,16 @@
           <t>9564329365-069-116035673894</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Milorizast</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Milorizast detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve">ALPHA PHARMA INDUSTRY </t>
@@ -1995,8 +2027,16 @@
           <t>9218183029-134-733665233550</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Novus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Novus detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -2182,8 +2222,16 @@
           <t>4281783679-596-964848105484</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Novus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Novus detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -2560,8 +2608,16 @@
           <t>9065897594-072-320096952459</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SoiCarby</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>SoiCarby detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -3499,8 +3555,16 @@
           <t>5317255652-368-279862322264</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CIBINQO</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>CIBINQO detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -4092,8 +4156,16 @@
           <t>1736478719-523-366158748158</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Fenofibrate Ethypharm</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Fenofibrate Ethypharm detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4273,8 +4345,16 @@
           <t>6348708216-037-028924383915</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lenvatinib BOS</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Lenvatinib BOS detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -4462,8 +4542,16 @@
           <t>1673820425-914-217800230130</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Hulio</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Hulio detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -4651,8 +4739,16 @@
           <t>1141518044-240-816246909752</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Hulio</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Hulio detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -4840,8 +4936,16 @@
           <t>8429604811-949-951149193166</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Nicorette Freshmint Gum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Nicorette Freshmint Gum detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -5031,8 +5135,16 @@
           <t>2843715327-803-425151378830</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Nicorette Freshmint Gum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Nicorette Freshmint Gum detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5218,8 +5330,16 @@
           <t>5080660351-512-284220855255</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Adacter</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Adacter detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5598,8 +5718,16 @@
           <t>9891092525-453-968766885252</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Inogara</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Inogara detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -5783,8 +5911,16 @@
           <t>9921668982-648-819055129634</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Apilipx</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Apilipx detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -5972,8 +6108,16 @@
           <t>6448933799-457-285493300556</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Apilipx</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Apilipx detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -6161,8 +6305,16 @@
           <t>9013124342-997-718867309527</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Apilipx</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Apilipx detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -6342,8 +6494,16 @@
           <t>2484634510-371-031397650325</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Apilipx</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Apilipx detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -6527,8 +6687,16 @@
           <t>9226190133-492-416913168936</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Clodipan 8 mg and 5mg</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Clodipan 8 mg and 5mg detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -6714,8 +6882,16 @@
           <t>8383723483-496-014750297520</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Clodipan 16 mg and 5 mg</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Clodipan 16 mg and 5 mg detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -6909,8 +7085,16 @@
           <t>1827995584-377-326075665484</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AMLOCARD 10 mg tablets</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>AMLOCARD 10 mg tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7088,8 +7272,16 @@
           <t>2624043822-953-608624817777</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Cekea</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Cekea detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7460,8 +7652,16 @@
           <t>2155943733-453-615338960393</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Welireg</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Welireg detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -8431,8 +8631,16 @@
           <t>9459897949-050-028867054337</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ursofalk</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Ursofalk detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -8819,8 +9027,16 @@
           <t>9359994450-149-262956898396</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pelgraz 6 mg in 0.6 ml</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Pelgraz 6 mg in 0.6 ml detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -9008,8 +9224,16 @@
           <t>4317504729-407-828325082689</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pantrox</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Pantrox detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9199,8 +9423,16 @@
           <t>4025083727-817-090723917985</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pantrox</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Pantrox detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9390,8 +9622,16 @@
           <t>4285590925-837-026755218203</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pantrox</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Pantrox detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -9577,8 +9817,16 @@
           <t>7929678073-052-097048678735</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Triplixam</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Triplixam detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -9768,8 +10016,16 @@
           <t>9661140143-503-317087983923</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Triplixam</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Triplixam detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -9955,8 +10211,16 @@
           <t>5232375087-802-052975853687</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Triplixam</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Triplixam detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10142,8 +10406,16 @@
           <t>9535470185-498-700747960063</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Triplixam</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Triplixam detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10329,8 +10601,16 @@
           <t>9666946339-780-229440233870</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tadalafil EVA</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Tadalafil EVA detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10514,8 +10794,16 @@
           <t>8635866305-210-886780709808</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Nevotic</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Nevotic detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -10705,8 +10993,16 @@
           <t>0753009683-230-888387606764</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Nexium 10 mg</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Nexium 10 mg detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -11091,8 +11387,16 @@
           <t>9195778485-047-499848126438</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tiomist</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Tiomist detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11280,8 +11584,16 @@
           <t>5735311672-737-722090719867</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Paxas</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Paxas detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11465,8 +11777,16 @@
           <t>5621632293-406-808355363875</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Paxas</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Paxas detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -11646,8 +11966,16 @@
           <t>4907240221-437-239776098656</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Paxas</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Paxas detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -11831,8 +12159,16 @@
           <t>0655969771-359-841030158501</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Daroxime</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Daroxime detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12016,8 +12352,16 @@
           <t>5880198049-660-697886924024</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Enoxaparin BOS</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Enoxaparin BOS detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -12209,8 +12553,16 @@
           <t>7472298984-525-464807631241</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Enoxaparin BOS</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Enoxaparin BOS detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -12398,8 +12750,16 @@
           <t>2489664388-164-654207211240</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Enoxaparin BOS</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Enoxaparin BOS detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -12587,8 +12947,16 @@
           <t>1879198503-775-472435334978</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Enoxaparin BOS</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Enoxaparin BOS detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -13357,8 +13725,16 @@
           <t>3375857710-062-487344990762</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Onstera</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Onstera detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13544,8 +13920,16 @@
           <t>9816274374-450-852264374825</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Verotec</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Verotec detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -13729,8 +14113,16 @@
           <t>5295006775-728-708159351000</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Verotec</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Verotec detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -13914,8 +14306,16 @@
           <t>1563985458-852-118207958054</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Verotec</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Verotec detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -14099,8 +14499,16 @@
           <t>6534529724-382-725167872543</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ranexa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Ranexa detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -14286,8 +14694,16 @@
           <t>5249218185-955-184678144324</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ranexa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Ranexa detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14471,8 +14887,16 @@
           <t>1662850560-724-546978629061</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ranexa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Ranexa detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -16228,8 +16652,16 @@
           <t>3592951936-746-513477814504</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lertiv</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Lertiv detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16419,8 +16851,16 @@
           <t>8797354683-994-545810343327</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lertiv</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Lertiv detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -17000,8 +17440,16 @@
           <t>5585650363-908-924429947227</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GONAL-f 150 IU per 0.25 ml</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>GONAL-f 150 IU per 0.25 ml detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17187,8 +17635,16 @@
           <t>4460012517-767-499812613294</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pantrox</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Pantrox detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17370,8 +17826,16 @@
           <t>2117253100-556-516497635327</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pafazin</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Pafazin detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
           <t>Pharma Pharmaceutical Industries (PPI)</t>
@@ -17559,8 +18023,16 @@
           <t>0506994601-391-477384712011</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pafazin</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Pafazin detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
           <t>Pharma Pharmaceutical Industries (PPI)</t>
@@ -17742,8 +18214,16 @@
           <t>8957252460-510-480212422601</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zodinex</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Zodinex detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -18118,8 +18598,16 @@
           <t>6181591382-027-805371443925</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pliaglis 15 gram Cream</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Pliaglis 15 gram Cream detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18305,8 +18793,16 @@
           <t>1690079112-624-942002601019</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pliaglis 30 gram Cream</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Pliaglis 30 gram Cream detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -18685,8 +19181,16 @@
           <t>9777146217-377-924471688668</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Donifoxate</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Donifoxate detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -18868,8 +19372,16 @@
           <t>0966974774-638-015090163806</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LERHASA</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>LERHASA detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
           <t xml:space="preserve">ALPHA PHARMA INDUSTRY </t>
@@ -19053,8 +19565,16 @@
           <t>4770813510-723-195380390892</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zeposia</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Zeposia detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -19238,8 +19758,16 @@
           <t>1017787242-491-502550765005</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zeposia (initiation pack) 4 caps 0.23 mg and 3 caps 0.46 mg</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Zeposia (initiation pack) 4 caps 0.23 mg and 3 caps 0.46 mg detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
@@ -19427,8 +19955,16 @@
           <t>3843018939-972-169399213310</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Esqua</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Esqua detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/54/file.xlsx
+++ b/product_upload/packages/54/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20176,7 +20176,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -21798,7 +21798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21879,40 +21879,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -21992,38 +21997,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>89.88</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-A916868F0F8D</t>
         </is>
@@ -22103,38 +22113,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>454.31</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-FA2CF3107700</t>
         </is>
@@ -22214,38 +22229,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>378.71</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-371E51D68655</t>
         </is>
@@ -22325,38 +22345,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>147.97</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-397FC4AC7964</t>
         </is>
@@ -22436,38 +22461,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>220.3</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-272501DB813A</t>
         </is>
@@ -22547,38 +22577,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>344.97</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-3C4CE9948E62</t>
         </is>
@@ -22658,38 +22693,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>356.89</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-A1F8F0539802</t>
         </is>
@@ -22769,38 +22809,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>476.57</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-C14BE86D7975</t>
         </is>
@@ -22880,38 +22925,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>183.66</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-67CA6B0AFC6C</t>
         </is>
@@ -22991,38 +23041,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>122.72</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-E1AF077774E1</t>
         </is>
@@ -23102,38 +23157,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>398.51</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-260FF45EB9B9</t>
         </is>
@@ -23213,38 +23273,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>63.31</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-38CA5EE42525</t>
         </is>
@@ -23324,38 +23389,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>241.69</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-DB835FA7AFB0</t>
         </is>
@@ -23435,38 +23505,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>323.53</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-F900AFBDC2B9</t>
         </is>
@@ -23546,38 +23621,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>99.08</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-D9B3452AFCC0</t>
         </is>
@@ -23657,38 +23737,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>451.59</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-F906AEDB8F6C</t>
         </is>
@@ -23768,38 +23853,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>92.92</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-029B56BE550F</t>
         </is>
@@ -23879,38 +23969,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>315.91</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-E99048D089B8</t>
         </is>
@@ -23990,38 +24085,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>447.02</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-D37CB09A359E</t>
         </is>
@@ -24101,38 +24201,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>341.19</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-F223EB776CAD</t>
         </is>
